--- a/data/log1.xlsx
+++ b/data/log1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dereck/Code/pingan/data-process/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2ABE71E6-BC75-C142-8A47-22C602CCA06F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6CA3E2C2-B25B-5841-A85B-A12C64725F6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="3220" yWindow="2200" windowWidth="28100" windowHeight="17360" xr2:uid="{66E88616-0BC8-B34A-BC5C-CB34DEFA5F1B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>record_id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -67,6 +67,18 @@
   </si>
   <si>
     <t>我有哪些持仓？</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>zzzz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>理赔比例</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>修改收获地址</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -451,7 +463,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E73004A-3272-844C-A883-0C0966A98AB8}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16"/>
   <sheetData>
     <row r="1" spans="1:2">
@@ -484,6 +496,22 @@
       </c>
       <c r="B4" t="s">
         <v>7</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>21</v>
+      </c>
+      <c r="B6" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
